--- a/VM2026_Tipping_Rolf.xlsx
+++ b/VM2026_Tipping_Rolf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Privat\31.Fotball\2026 - VM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://consafelogistics-my.sharepoint.com/personal/martin_skaug_consafelogistics_com/Documents/Desktop/VM/Tipping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FDAFAC-4FBE-4837-BDBC-3E9B014C2C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{E2FDAFAC-4FBE-4837-BDBC-3E9B014C2C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A969F9CB-D848-4229-A79C-1A572448EB65}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MINE TIPS" sheetId="1" r:id="rId1"/>
@@ -548,7 +548,7 @@
     <t>Makedonia</t>
   </si>
   <si>
-    <t>The Rolf</t>
+    <t>Rolf</t>
   </si>
 </sst>
 </file>
@@ -1507,6 +1507,42 @@
     <xf numFmtId="0" fontId="14" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1521,42 +1557,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2097,20 +2097,20 @@
     <tabColor rgb="FFE94560"/>
   </sheetPr>
   <dimension ref="A1:AF367"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" customWidth="1"/>
-    <col min="12" max="12" width="1.5703125" customWidth="1"/>
+    <col min="11" max="11" width="6.88671875" customWidth="1"/>
+    <col min="12" max="12" width="1.5546875" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
     <col min="14" max="17" width="4" customWidth="1"/>
     <col min="18" max="21" width="5" customWidth="1"/>
@@ -2118,114 +2118,114 @@
     <col min="23" max="32" width="18" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="M1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-    </row>
-    <row r="2" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+    <row r="1" spans="1:32" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="M1" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+    </row>
+    <row r="2" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="56" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="68" t="s">
         <v>169</v>
       </c>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="M2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-    </row>
-    <row r="3" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="M2" s="69" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+    </row>
+    <row r="3" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="M3" s="59" t="s">
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="M3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
-      <c r="U3" s="59"/>
-    </row>
-    <row r="4" spans="1:32" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+    </row>
+    <row r="4" spans="1:32" ht="4.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="M5" s="61" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="M5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="61"/>
-    </row>
-    <row r="6" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+    </row>
+    <row r="6" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>2</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>6</v>
       </c>
@@ -2795,33 +2795,33 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="60" t="s">
+    <row r="13" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="M13" s="61" t="s">
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="M13" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61"/>
-      <c r="T13" s="61"/>
-      <c r="U13" s="61"/>
-    </row>
-    <row r="14" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="57"/>
+    </row>
+    <row r="14" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>7</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>8</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>9</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>10</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>11</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>12</v>
       </c>
@@ -3391,33 +3391,33 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="60" t="s">
+    <row r="21" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="M21" s="61" t="s">
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="M21" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="N21" s="61"/>
-      <c r="O21" s="61"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="61"/>
-      <c r="R21" s="61"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="61"/>
-    </row>
-    <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
+    </row>
+    <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>14</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>16</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>17</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>18</v>
       </c>
@@ -3987,33 +3987,33 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="60" t="s">
+    <row r="29" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="60"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="60"/>
-      <c r="M29" s="61" t="s">
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="56"/>
+      <c r="M29" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="N29" s="61"/>
-      <c r="O29" s="61"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="61"/>
-      <c r="R29" s="61"/>
-      <c r="S29" s="61"/>
-      <c r="T29" s="61"/>
-      <c r="U29" s="61"/>
-    </row>
-    <row r="30" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="57"/>
+      <c r="S29" s="57"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="57"/>
+    </row>
+    <row r="30" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>8</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>19</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>20</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>21</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>22</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>23</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>24</v>
       </c>
@@ -4583,33 +4583,33 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="60" t="s">
+    <row r="37" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="60"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="60"/>
-      <c r="M37" s="61" t="s">
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="M37" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="N37" s="61"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="61"/>
-      <c r="R37" s="61"/>
-      <c r="S37" s="61"/>
-      <c r="T37" s="61"/>
-      <c r="U37" s="61"/>
-    </row>
-    <row r="38" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+    </row>
+    <row r="38" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>8</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>25</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>26</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>27</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>28</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>29</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>30</v>
       </c>
@@ -5179,33 +5179,33 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="60" t="s">
+    <row r="45" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="60"/>
-      <c r="F45" s="60"/>
-      <c r="G45" s="60"/>
-      <c r="H45" s="60"/>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="60"/>
-      <c r="M45" s="61" t="s">
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="56"/>
+      <c r="K45" s="56"/>
+      <c r="M45" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="N45" s="61"/>
-      <c r="O45" s="61"/>
-      <c r="P45" s="61"/>
-      <c r="Q45" s="61"/>
-      <c r="R45" s="61"/>
-      <c r="S45" s="61"/>
-      <c r="T45" s="61"/>
-      <c r="U45" s="61"/>
-    </row>
-    <row r="46" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N45" s="57"/>
+      <c r="O45" s="57"/>
+      <c r="P45" s="57"/>
+      <c r="Q45" s="57"/>
+      <c r="R45" s="57"/>
+      <c r="S45" s="57"/>
+      <c r="T45" s="57"/>
+      <c r="U45" s="57"/>
+    </row>
+    <row r="46" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>8</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>31</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>32</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>33</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>34</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>35</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>36</v>
       </c>
@@ -5775,33 +5775,33 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="60" t="s">
+    <row r="53" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="B53" s="60"/>
-      <c r="C53" s="60"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="60"/>
-      <c r="F53" s="60"/>
-      <c r="G53" s="60"/>
-      <c r="H53" s="60"/>
-      <c r="I53" s="60"/>
-      <c r="J53" s="60"/>
-      <c r="K53" s="60"/>
-      <c r="M53" s="61" t="s">
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
+      <c r="M53" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="N53" s="61"/>
-      <c r="O53" s="61"/>
-      <c r="P53" s="61"/>
-      <c r="Q53" s="61"/>
-      <c r="R53" s="61"/>
-      <c r="S53" s="61"/>
-      <c r="T53" s="61"/>
-      <c r="U53" s="61"/>
-    </row>
-    <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N53" s="57"/>
+      <c r="O53" s="57"/>
+      <c r="P53" s="57"/>
+      <c r="Q53" s="57"/>
+      <c r="R53" s="57"/>
+      <c r="S53" s="57"/>
+      <c r="T53" s="57"/>
+      <c r="U53" s="57"/>
+    </row>
+    <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>8</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>37</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>38</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>39</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>40</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>41</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>42</v>
       </c>
@@ -6371,33 +6371,33 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="60" t="s">
+    <row r="61" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="60"/>
-      <c r="C61" s="60"/>
-      <c r="D61" s="60"/>
-      <c r="E61" s="60"/>
-      <c r="F61" s="60"/>
-      <c r="G61" s="60"/>
-      <c r="H61" s="60"/>
-      <c r="I61" s="60"/>
-      <c r="J61" s="60"/>
-      <c r="K61" s="60"/>
-      <c r="M61" s="61" t="s">
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56"/>
+      <c r="K61" s="56"/>
+      <c r="M61" s="57" t="s">
         <v>121</v>
       </c>
-      <c r="N61" s="61"/>
-      <c r="O61" s="61"/>
-      <c r="P61" s="61"/>
-      <c r="Q61" s="61"/>
-      <c r="R61" s="61"/>
-      <c r="S61" s="61"/>
-      <c r="T61" s="61"/>
-      <c r="U61" s="61"/>
-    </row>
-    <row r="62" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N61" s="57"/>
+      <c r="O61" s="57"/>
+      <c r="P61" s="57"/>
+      <c r="Q61" s="57"/>
+      <c r="R61" s="57"/>
+      <c r="S61" s="57"/>
+      <c r="T61" s="57"/>
+      <c r="U61" s="57"/>
+    </row>
+    <row r="62" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>8</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>43</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>44</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>45</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>46</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>47</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>48</v>
       </c>
@@ -6967,33 +6967,33 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="62" t="s">
+    <row r="69" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="B69" s="62"/>
-      <c r="C69" s="62"/>
-      <c r="D69" s="62"/>
-      <c r="E69" s="62"/>
-      <c r="F69" s="62"/>
-      <c r="G69" s="62"/>
-      <c r="H69" s="62"/>
-      <c r="I69" s="62"/>
-      <c r="J69" s="62"/>
-      <c r="K69" s="62"/>
-      <c r="M69" s="63" t="s">
+      <c r="B69" s="61"/>
+      <c r="C69" s="61"/>
+      <c r="D69" s="61"/>
+      <c r="E69" s="61"/>
+      <c r="F69" s="61"/>
+      <c r="G69" s="61"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="61"/>
+      <c r="J69" s="61"/>
+      <c r="K69" s="61"/>
+      <c r="M69" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="N69" s="63"/>
-      <c r="O69" s="63"/>
-      <c r="P69" s="63"/>
-      <c r="Q69" s="63"/>
-      <c r="R69" s="63"/>
-      <c r="S69" s="63"/>
-      <c r="T69" s="63"/>
-      <c r="U69" s="63"/>
-    </row>
-    <row r="70" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N69" s="62"/>
+      <c r="O69" s="62"/>
+      <c r="P69" s="62"/>
+      <c r="Q69" s="62"/>
+      <c r="R69" s="62"/>
+      <c r="S69" s="62"/>
+      <c r="T69" s="62"/>
+      <c r="U69" s="62"/>
+    </row>
+    <row r="70" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>8</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>49</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>50</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>51</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>52</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>53</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>54</v>
       </c>
@@ -7563,33 +7563,33 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="60" t="s">
+    <row r="77" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="56" t="s">
         <v>137</v>
       </c>
-      <c r="B77" s="60"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="60"/>
-      <c r="F77" s="60"/>
-      <c r="G77" s="60"/>
-      <c r="H77" s="60"/>
-      <c r="I77" s="60"/>
-      <c r="J77" s="60"/>
-      <c r="K77" s="60"/>
-      <c r="M77" s="61" t="s">
+      <c r="B77" s="56"/>
+      <c r="C77" s="56"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="56"/>
+      <c r="H77" s="56"/>
+      <c r="I77" s="56"/>
+      <c r="J77" s="56"/>
+      <c r="K77" s="56"/>
+      <c r="M77" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="N77" s="61"/>
-      <c r="O77" s="61"/>
-      <c r="P77" s="61"/>
-      <c r="Q77" s="61"/>
-      <c r="R77" s="61"/>
-      <c r="S77" s="61"/>
-      <c r="T77" s="61"/>
-      <c r="U77" s="61"/>
-    </row>
-    <row r="78" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N77" s="57"/>
+      <c r="O77" s="57"/>
+      <c r="P77" s="57"/>
+      <c r="Q77" s="57"/>
+      <c r="R77" s="57"/>
+      <c r="S77" s="57"/>
+      <c r="T77" s="57"/>
+      <c r="U77" s="57"/>
+    </row>
+    <row r="78" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>8</v>
       </c>
@@ -7649,7 +7649,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>55</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>56</v>
       </c>
@@ -7869,7 +7869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>57</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>58</v>
       </c>
@@ -8089,7 +8089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>59</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>60</v>
       </c>
@@ -8159,33 +8159,33 @@
         <v>40</v>
       </c>
     </row>
-    <row r="85" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="60" t="s">
+    <row r="85" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="B85" s="60"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
-      <c r="E85" s="60"/>
-      <c r="F85" s="60"/>
-      <c r="G85" s="60"/>
-      <c r="H85" s="60"/>
-      <c r="I85" s="60"/>
-      <c r="J85" s="60"/>
-      <c r="K85" s="60"/>
-      <c r="M85" s="61" t="s">
+      <c r="B85" s="56"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56"/>
+      <c r="J85" s="56"/>
+      <c r="K85" s="56"/>
+      <c r="M85" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="N85" s="61"/>
-      <c r="O85" s="61"/>
-      <c r="P85" s="61"/>
-      <c r="Q85" s="61"/>
-      <c r="R85" s="61"/>
-      <c r="S85" s="61"/>
-      <c r="T85" s="61"/>
-      <c r="U85" s="61"/>
-    </row>
-    <row r="86" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N85" s="57"/>
+      <c r="O85" s="57"/>
+      <c r="P85" s="57"/>
+      <c r="Q85" s="57"/>
+      <c r="R85" s="57"/>
+      <c r="S85" s="57"/>
+      <c r="T85" s="57"/>
+      <c r="U85" s="57"/>
+    </row>
+    <row r="86" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>8</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>61</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>62</v>
       </c>
@@ -8465,7 +8465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>63</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>64</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>65</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>66</v>
       </c>
@@ -8755,33 +8755,33 @@
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="60" t="s">
+    <row r="93" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="B93" s="60"/>
-      <c r="C93" s="60"/>
-      <c r="D93" s="60"/>
-      <c r="E93" s="60"/>
-      <c r="F93" s="60"/>
-      <c r="G93" s="60"/>
-      <c r="H93" s="60"/>
-      <c r="I93" s="60"/>
-      <c r="J93" s="60"/>
-      <c r="K93" s="60"/>
-      <c r="M93" s="61" t="s">
+      <c r="B93" s="56"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="56"/>
+      <c r="G93" s="56"/>
+      <c r="H93" s="56"/>
+      <c r="I93" s="56"/>
+      <c r="J93" s="56"/>
+      <c r="K93" s="56"/>
+      <c r="M93" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="N93" s="61"/>
-      <c r="O93" s="61"/>
-      <c r="P93" s="61"/>
-      <c r="Q93" s="61"/>
-      <c r="R93" s="61"/>
-      <c r="S93" s="61"/>
-      <c r="T93" s="61"/>
-      <c r="U93" s="61"/>
-    </row>
-    <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N93" s="57"/>
+      <c r="O93" s="57"/>
+      <c r="P93" s="57"/>
+      <c r="Q93" s="57"/>
+      <c r="R93" s="57"/>
+      <c r="S93" s="57"/>
+      <c r="T93" s="57"/>
+      <c r="U93" s="57"/>
+    </row>
+    <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>8</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>67</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>68</v>
       </c>
@@ -9061,7 +9061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>69</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>70</v>
       </c>
@@ -9281,7 +9281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>71</v>
       </c>
@@ -9316,7 +9316,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>72</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="101" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -9359,12 +9359,12 @@
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
       <c r="G101" s="12"/>
-      <c r="H101" s="67" t="s">
+      <c r="H101" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="I101" s="67"/>
-      <c r="J101" s="67"/>
-      <c r="K101" s="67"/>
+      <c r="I101" s="58"/>
+      <c r="J101" s="58"/>
+      <c r="K101" s="58"/>
       <c r="L101" s="12"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12"/>
@@ -9386,7 +9386,7 @@
       <c r="AD101" s="12"/>
       <c r="AE101" s="12"/>
     </row>
-    <row r="102" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -9421,7 +9421,7 @@
       <c r="AD102" s="12"/>
       <c r="AE102" s="12"/>
     </row>
-    <row r="103" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -9430,11 +9430,11 @@
       <c r="F103" s="12"/>
       <c r="G103" s="12"/>
       <c r="H103" s="14"/>
-      <c r="I103" s="68" t="s">
+      <c r="I103" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="J103" s="68"/>
-      <c r="K103" s="68"/>
+      <c r="J103" s="59"/>
+      <c r="K103" s="59"/>
       <c r="L103" s="12"/>
       <c r="M103" s="12"/>
       <c r="N103" s="12"/>
@@ -9456,7 +9456,7 @@
       <c r="AD103" s="12"/>
       <c r="AE103" s="12"/>
     </row>
-    <row r="104" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -9466,7 +9466,7 @@
       <c r="G104" s="12"/>
       <c r="H104" s="15" t="str">
         <f>COUNTIF(H105:H136,1)&amp;"/16"</f>
-        <v>1/16</v>
+        <v>16/16</v>
       </c>
       <c r="I104" s="16" t="s">
         <v>18</v>
@@ -9494,7 +9494,7 @@
       <c r="AD104" s="12"/>
       <c r="AE104" s="12"/>
     </row>
-    <row r="105" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -9537,7 +9537,7 @@
       <c r="AD105" s="12"/>
       <c r="AE105" s="12"/>
     </row>
-    <row r="106" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -9576,7 +9576,7 @@
       <c r="AD106" s="12"/>
       <c r="AE106" s="12"/>
     </row>
-    <row r="107" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -9585,7 +9585,7 @@
       <c r="F107" s="12"/>
       <c r="G107" s="12"/>
       <c r="H107" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I107" s="19" t="str">
         <f>IFERROR(M15,"B1")</f>
@@ -9618,7 +9618,7 @@
       <c r="AD107" s="12"/>
       <c r="AE107" s="12"/>
     </row>
-    <row r="108" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -9657,7 +9657,7 @@
       <c r="AD108" s="12"/>
       <c r="AE108" s="12"/>
     </row>
-    <row r="109" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -9666,7 +9666,7 @@
       <c r="F109" s="12"/>
       <c r="G109" s="12"/>
       <c r="H109" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I109" s="19" t="str">
         <f>IFERROR(M23,"C1")</f>
@@ -9699,7 +9699,7 @@
       <c r="AD109" s="12"/>
       <c r="AE109" s="12"/>
     </row>
-    <row r="110" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -9708,7 +9708,7 @@
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
       <c r="H110" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I110" s="22" t="str">
         <f>IFERROR(M24,"C2")</f>
@@ -9741,7 +9741,7 @@
       <c r="AD110" s="12"/>
       <c r="AE110" s="12"/>
     </row>
-    <row r="111" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -9780,7 +9780,7 @@
       <c r="AD111" s="12"/>
       <c r="AE111" s="12"/>
     </row>
-    <row r="112" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -9789,7 +9789,7 @@
       <c r="F112" s="12"/>
       <c r="G112" s="12"/>
       <c r="H112" s="21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I112" s="22" t="str">
         <f>IFERROR(M32,"D2")</f>
@@ -9822,7 +9822,7 @@
       <c r="AD112" s="12"/>
       <c r="AE112" s="12"/>
     </row>
-    <row r="113" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -9831,7 +9831,7 @@
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
       <c r="H113" s="18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I113" s="19" t="str">
         <f>IFERROR(M39,"E1")</f>
@@ -9864,7 +9864,7 @@
       <c r="AD113" s="12"/>
       <c r="AE113" s="12"/>
     </row>
-    <row r="114" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -9903,7 +9903,7 @@
       <c r="AD114" s="12"/>
       <c r="AE114" s="12"/>
     </row>
-    <row r="115" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -9912,7 +9912,7 @@
       <c r="F115" s="12"/>
       <c r="G115" s="12"/>
       <c r="H115" s="18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I115" s="19" t="str">
         <f>IFERROR(M47,"F1")</f>
@@ -9945,7 +9945,7 @@
       <c r="AD115" s="12"/>
       <c r="AE115" s="12"/>
     </row>
-    <row r="116" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -9984,7 +9984,7 @@
       <c r="AD116" s="12"/>
       <c r="AE116" s="12"/>
     </row>
-    <row r="117" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -9993,7 +9993,7 @@
       <c r="F117" s="12"/>
       <c r="G117" s="12"/>
       <c r="H117" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I117" s="19" t="str">
         <f>IFERROR(M55,"G1")</f>
@@ -10026,7 +10026,7 @@
       <c r="AD117" s="12"/>
       <c r="AE117" s="12"/>
     </row>
-    <row r="118" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -10035,7 +10035,7 @@
       <c r="F118" s="12"/>
       <c r="G118" s="12"/>
       <c r="H118" s="21">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I118" s="22" t="str">
         <f>IFERROR(M56,"G2")</f>
@@ -10068,7 +10068,7 @@
       <c r="AD118" s="12"/>
       <c r="AE118" s="12"/>
     </row>
-    <row r="119" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -10077,7 +10077,7 @@
       <c r="F119" s="12"/>
       <c r="G119" s="12"/>
       <c r="H119" s="18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I119" s="19" t="str">
         <f>IFERROR(M63,"H1")</f>
@@ -10110,7 +10110,7 @@
       <c r="AD119" s="12"/>
       <c r="AE119" s="12"/>
     </row>
-    <row r="120" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -10149,7 +10149,7 @@
       <c r="AD120" s="12"/>
       <c r="AE120" s="12"/>
     </row>
-    <row r="121" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -10158,7 +10158,7 @@
       <c r="F121" s="12"/>
       <c r="G121" s="12"/>
       <c r="H121" s="18">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I121" s="19" t="str">
         <f>IFERROR(M71,"I1")</f>
@@ -10191,7 +10191,7 @@
       <c r="AD121" s="12"/>
       <c r="AE121" s="12"/>
     </row>
-    <row r="122" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="12"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
@@ -10230,7 +10230,7 @@
       <c r="AD122" s="12"/>
       <c r="AE122" s="12"/>
     </row>
-    <row r="123" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="12"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
@@ -10239,7 +10239,7 @@
       <c r="F123" s="12"/>
       <c r="G123" s="12"/>
       <c r="H123" s="18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I123" s="19" t="str">
         <f>IFERROR(M79,"J1")</f>
@@ -10272,7 +10272,7 @@
       <c r="AD123" s="12"/>
       <c r="AE123" s="12"/>
     </row>
-    <row r="124" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="12"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
@@ -10311,7 +10311,7 @@
       <c r="AD124" s="12"/>
       <c r="AE124" s="12"/>
     </row>
-    <row r="125" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
@@ -10320,7 +10320,7 @@
       <c r="F125" s="12"/>
       <c r="G125" s="12"/>
       <c r="H125" s="18">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I125" s="19" t="str">
         <f>IFERROR(M87,"K1")</f>
@@ -10353,7 +10353,7 @@
       <c r="AD125" s="12"/>
       <c r="AE125" s="12"/>
     </row>
-    <row r="126" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -10392,7 +10392,7 @@
       <c r="AD126" s="12"/>
       <c r="AE126" s="12"/>
     </row>
-    <row r="127" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
@@ -10401,7 +10401,7 @@
       <c r="F127" s="12"/>
       <c r="G127" s="12"/>
       <c r="H127" s="18">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I127" s="19" t="str">
         <f>IFERROR(M95,"L1")</f>
@@ -10434,7 +10434,7 @@
       <c r="AD127" s="12"/>
       <c r="AE127" s="12"/>
     </row>
-    <row r="128" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
@@ -10443,7 +10443,7 @@
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
       <c r="H128" s="21">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I128" s="22" t="str">
         <f>IFERROR(M96,"L2")</f>
@@ -10476,7 +10476,7 @@
       <c r="AD128" s="12"/>
       <c r="AE128" s="12"/>
     </row>
-    <row r="129" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -10485,7 +10485,7 @@
       <c r="F129" s="12"/>
       <c r="G129" s="12"/>
       <c r="H129" s="18">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I129" s="19" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(1,$E$300:$E$311,0)),"")</f>
@@ -10518,7 +10518,7 @@
       <c r="AD129" s="12"/>
       <c r="AE129" s="12"/>
     </row>
-    <row r="130" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -10556,7 +10556,7 @@
       <c r="AD130" s="12"/>
       <c r="AE130" s="12"/>
     </row>
-    <row r="131" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
@@ -10595,7 +10595,7 @@
       <c r="AD131" s="12"/>
       <c r="AE131" s="12"/>
     </row>
-    <row r="132" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
@@ -10634,7 +10634,7 @@
       <c r="AD132" s="12"/>
       <c r="AE132" s="12"/>
     </row>
-    <row r="133" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
@@ -10673,7 +10673,7 @@
       <c r="AD133" s="12"/>
       <c r="AE133" s="12"/>
     </row>
-    <row r="134" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -10712,7 +10712,7 @@
       <c r="AD134" s="12"/>
       <c r="AE134" s="12"/>
     </row>
-    <row r="135" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -10751,7 +10751,7 @@
       <c r="AD135" s="12"/>
       <c r="AE135" s="12"/>
     </row>
-    <row r="136" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -10790,7 +10790,7 @@
       <c r="AD136" s="12"/>
       <c r="AE136" s="12"/>
     </row>
-    <row r="137" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
@@ -10823,7 +10823,7 @@
       <c r="AD137" s="12"/>
       <c r="AE137" s="12"/>
     </row>
-    <row r="138" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>
@@ -10832,11 +10832,11 @@
       <c r="F138" s="12"/>
       <c r="G138" s="12"/>
       <c r="H138" s="25"/>
-      <c r="I138" s="69" t="s">
+      <c r="I138" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="J138" s="69"/>
-      <c r="K138" s="69"/>
+      <c r="J138" s="60"/>
+      <c r="K138" s="60"/>
       <c r="L138" s="12"/>
       <c r="M138" s="12"/>
       <c r="N138" s="12"/>
@@ -10858,7 +10858,7 @@
       <c r="AD138" s="12"/>
       <c r="AE138" s="12"/>
     </row>
-    <row r="139" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -10868,7 +10868,7 @@
       <c r="G139" s="12"/>
       <c r="H139" s="15" t="str">
         <f>COUNTIF(H140:H155,1)&amp;"/8"</f>
-        <v>1/8</v>
+        <v>8/8</v>
       </c>
       <c r="I139" s="16" t="s">
         <v>18</v>
@@ -10896,7 +10896,7 @@
       <c r="AD139" s="12"/>
       <c r="AE139" s="12"/>
     </row>
-    <row r="140" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -10936,7 +10936,7 @@
       <c r="AD140" s="12"/>
       <c r="AE140" s="12"/>
     </row>
-    <row r="141" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
@@ -10945,7 +10945,7 @@
       <c r="F141" s="12"/>
       <c r="G141" s="12"/>
       <c r="H141" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I141" s="30" t="s">
         <v>89</v>
@@ -10975,7 +10975,7 @@
       <c r="AD141" s="12"/>
       <c r="AE141" s="12"/>
     </row>
-    <row r="142" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
@@ -10984,7 +10984,7 @@
       <c r="F142" s="12"/>
       <c r="G142" s="12"/>
       <c r="H142" s="26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I142" s="27" t="s">
         <v>123</v>
@@ -11014,7 +11014,7 @@
       <c r="AD142" s="12"/>
       <c r="AE142" s="12"/>
     </row>
-    <row r="143" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12"/>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
@@ -11023,7 +11023,7 @@
       <c r="F143" s="12"/>
       <c r="G143" s="12"/>
       <c r="H143" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I143" s="30" t="s">
         <v>67</v>
@@ -11053,7 +11053,7 @@
       <c r="AD143" s="12"/>
       <c r="AE143" s="12"/>
     </row>
-    <row r="144" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="12"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12"/>
@@ -11062,7 +11062,7 @@
       <c r="F144" s="12"/>
       <c r="G144" s="12"/>
       <c r="H144" s="26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I144" s="27" t="s">
         <v>140</v>
@@ -11092,7 +11092,7 @@
       <c r="AD144" s="12"/>
       <c r="AE144" s="12"/>
     </row>
-    <row r="145" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="12"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
@@ -11101,7 +11101,7 @@
       <c r="F145" s="12"/>
       <c r="G145" s="12"/>
       <c r="H145" s="29">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I145" s="30" t="s">
         <v>130</v>
@@ -11131,7 +11131,7 @@
       <c r="AD145" s="12"/>
       <c r="AE145" s="12"/>
     </row>
-    <row r="146" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
@@ -11140,7 +11140,7 @@
       <c r="F146" s="12"/>
       <c r="G146" s="12"/>
       <c r="H146" s="26">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I146" s="27" t="s">
         <v>112</v>
@@ -11170,7 +11170,7 @@
       <c r="AD146" s="12"/>
       <c r="AE146" s="12"/>
     </row>
-    <row r="147" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12"/>
@@ -11179,7 +11179,7 @@
       <c r="F147" s="12"/>
       <c r="G147" s="12"/>
       <c r="H147" s="29">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I147" s="30" t="s">
         <v>133</v>
@@ -11209,7 +11209,7 @@
       <c r="AD147" s="12"/>
       <c r="AE147" s="12"/>
     </row>
-    <row r="148" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12"/>
@@ -11245,7 +11245,7 @@
       <c r="AD148" s="12"/>
       <c r="AE148" s="12"/>
     </row>
-    <row r="149" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12"/>
@@ -11281,7 +11281,7 @@
       <c r="AD149" s="12"/>
       <c r="AE149" s="12"/>
     </row>
-    <row r="150" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
@@ -11317,7 +11317,7 @@
       <c r="AD150" s="12"/>
       <c r="AE150" s="12"/>
     </row>
-    <row r="151" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="12"/>
       <c r="B151" s="12"/>
       <c r="C151" s="12"/>
@@ -11353,7 +11353,7 @@
       <c r="AD151" s="12"/>
       <c r="AE151" s="12"/>
     </row>
-    <row r="152" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12"/>
       <c r="B152" s="12"/>
       <c r="C152" s="12"/>
@@ -11389,7 +11389,7 @@
       <c r="AD152" s="12"/>
       <c r="AE152" s="12"/>
     </row>
-    <row r="153" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12"/>
@@ -11425,7 +11425,7 @@
       <c r="AD153" s="12"/>
       <c r="AE153" s="12"/>
     </row>
-    <row r="154" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
@@ -11461,7 +11461,7 @@
       <c r="AD154" s="12"/>
       <c r="AE154" s="12"/>
     </row>
-    <row r="155" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="12"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
@@ -11497,7 +11497,7 @@
       <c r="AD155" s="12"/>
       <c r="AE155" s="12"/>
     </row>
-    <row r="156" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
@@ -11530,7 +11530,7 @@
       <c r="AD156" s="12"/>
       <c r="AE156" s="12"/>
     </row>
-    <row r="157" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="12"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12"/>
@@ -11539,11 +11539,11 @@
       <c r="F157" s="12"/>
       <c r="G157" s="12"/>
       <c r="H157" s="32"/>
-      <c r="I157" s="64" t="s">
+      <c r="I157" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="J157" s="64"/>
-      <c r="K157" s="64"/>
+      <c r="J157" s="53"/>
+      <c r="K157" s="53"/>
       <c r="L157" s="12"/>
       <c r="M157" s="12"/>
       <c r="N157" s="12"/>
@@ -11565,7 +11565,7 @@
       <c r="AD157" s="12"/>
       <c r="AE157" s="12"/>
     </row>
-    <row r="158" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="12"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12"/>
@@ -11575,7 +11575,7 @@
       <c r="G158" s="12"/>
       <c r="H158" s="15" t="str">
         <f>COUNTIF(H159:H166,1)&amp;"/4"</f>
-        <v>1/4</v>
+        <v>4/4</v>
       </c>
       <c r="I158" s="16" t="s">
         <v>18</v>
@@ -11603,7 +11603,7 @@
       <c r="AD158" s="12"/>
       <c r="AE158" s="12"/>
     </row>
-    <row r="159" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12"/>
@@ -11643,7 +11643,7 @@
       <c r="AD159" s="12"/>
       <c r="AE159" s="12"/>
     </row>
-    <row r="160" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12"/>
@@ -11652,14 +11652,14 @@
       <c r="F160" s="12"/>
       <c r="G160" s="12"/>
       <c r="H160" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I160" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="J160" s="12" t="str">
+      <c r="J160" s="12">
         <f>IF(H160=1,COUNTIF($H$159:H160,1),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K160" s="38"/>
       <c r="L160" s="12"/>
@@ -11683,7 +11683,7 @@
       <c r="AD160" s="12"/>
       <c r="AE160" s="12"/>
     </row>
-    <row r="161" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
@@ -11692,14 +11692,14 @@
       <c r="F161" s="12"/>
       <c r="G161" s="12"/>
       <c r="H161" s="33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I161" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="J161" s="12" t="str">
+      <c r="J161" s="12">
         <f>IF(H161=1,COUNTIF($H$159:H161,1),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K161" s="35"/>
       <c r="L161" s="12"/>
@@ -11723,7 +11723,7 @@
       <c r="AD161" s="12"/>
       <c r="AE161" s="12"/>
     </row>
-    <row r="162" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="12"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12"/>
@@ -11732,14 +11732,14 @@
       <c r="F162" s="12"/>
       <c r="G162" s="12"/>
       <c r="H162" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I162" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="J162" s="12" t="str">
+      <c r="J162" s="12">
         <f>IF(H162=1,COUNTIF($H$159:H162,1),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K162" s="38"/>
       <c r="L162" s="12"/>
@@ -11763,7 +11763,7 @@
       <c r="AD162" s="12"/>
       <c r="AE162" s="12"/>
     </row>
-    <row r="163" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="12"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12"/>
@@ -11799,7 +11799,7 @@
       <c r="AD163" s="12"/>
       <c r="AE163" s="12"/>
     </row>
-    <row r="164" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="12"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12"/>
@@ -11835,7 +11835,7 @@
       <c r="AD164" s="12"/>
       <c r="AE164" s="12"/>
     </row>
-    <row r="165" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="12"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12"/>
@@ -11871,7 +11871,7 @@
       <c r="AD165" s="12"/>
       <c r="AE165" s="12"/>
     </row>
-    <row r="166" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12"/>
@@ -11910,7 +11910,7 @@
       <c r="AD166" s="12"/>
       <c r="AE166" s="12"/>
     </row>
-    <row r="167" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="12"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12"/>
@@ -11943,7 +11943,7 @@
       <c r="AD167" s="12"/>
       <c r="AE167" s="12"/>
     </row>
-    <row r="168" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -11952,11 +11952,11 @@
       <c r="F168" s="12"/>
       <c r="G168" s="12"/>
       <c r="H168" s="39"/>
-      <c r="I168" s="65" t="s">
+      <c r="I168" s="54" t="s">
         <v>165</v>
       </c>
-      <c r="J168" s="65"/>
-      <c r="K168" s="65"/>
+      <c r="J168" s="54"/>
+      <c r="K168" s="54"/>
       <c r="L168" s="12"/>
       <c r="M168" s="12"/>
       <c r="N168" s="12"/>
@@ -11978,7 +11978,7 @@
       <c r="AD168" s="12"/>
       <c r="AE168" s="12"/>
     </row>
-    <row r="169" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12"/>
@@ -11988,7 +11988,7 @@
       <c r="G169" s="12"/>
       <c r="H169" s="15" t="str">
         <f>COUNTIF(H170:H173,1)&amp;"/2"</f>
-        <v>1/2</v>
+        <v>2/2</v>
       </c>
       <c r="I169" s="16" t="s">
         <v>18</v>
@@ -12016,7 +12016,7 @@
       <c r="AD169" s="12"/>
       <c r="AE169" s="12"/>
     </row>
-    <row r="170" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12"/>
@@ -12057,7 +12057,7 @@
       <c r="AD170" s="12"/>
       <c r="AE170" s="12"/>
     </row>
-    <row r="171" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12"/>
@@ -12066,7 +12066,7 @@
       <c r="F171" s="12"/>
       <c r="G171" s="12"/>
       <c r="H171" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I171" s="44" t="s">
         <v>123</v>
@@ -12096,7 +12096,7 @@
       <c r="AD171" s="12"/>
       <c r="AE171" s="12"/>
     </row>
-    <row r="172" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -12107,7 +12107,7 @@
       <c r="H172" s="40"/>
       <c r="I172" s="41" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(3,$J$159:$J$166,0)),"")</f>
-        <v/>
+        <v>Spania</v>
       </c>
       <c r="J172" s="12" t="str">
         <f>IF(H172=1,COUNTIF($H$170:H172,1),"")</f>
@@ -12135,7 +12135,7 @@
       <c r="AD172" s="12"/>
       <c r="AE172" s="12"/>
     </row>
-    <row r="173" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="12"/>
       <c r="B173" s="12"/>
       <c r="C173" s="12"/>
@@ -12146,7 +12146,7 @@
       <c r="H173" s="43"/>
       <c r="I173" s="44" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(4,$J$159:$J$166,0)),"")</f>
-        <v/>
+        <v>Norge</v>
       </c>
       <c r="J173" s="12" t="str">
         <f>IF(H173=1,COUNTIF($H$170:H173,1),"")</f>
@@ -12174,7 +12174,7 @@
       <c r="AD173" s="12"/>
       <c r="AE173" s="12"/>
     </row>
-    <row r="174" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="12"/>
       <c r="B174" s="12"/>
       <c r="C174" s="12"/>
@@ -12207,7 +12207,7 @@
       <c r="AD174" s="12"/>
       <c r="AE174" s="12"/>
     </row>
-    <row r="175" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="12"/>
       <c r="B175" s="12"/>
       <c r="C175" s="12"/>
@@ -12216,11 +12216,11 @@
       <c r="F175" s="12"/>
       <c r="G175" s="12"/>
       <c r="H175" s="46"/>
-      <c r="I175" s="66" t="s">
+      <c r="I175" s="55" t="s">
         <v>166</v>
       </c>
-      <c r="J175" s="66"/>
-      <c r="K175" s="66"/>
+      <c r="J175" s="55"/>
+      <c r="K175" s="55"/>
       <c r="L175" s="12"/>
       <c r="M175" s="12"/>
       <c r="N175" s="12"/>
@@ -12242,7 +12242,7 @@
       <c r="AD175" s="12"/>
       <c r="AE175" s="12"/>
     </row>
-    <row r="176" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12"/>
       <c r="B176" s="12"/>
       <c r="C176" s="12"/>
@@ -12280,7 +12280,7 @@
       <c r="AD176" s="12"/>
       <c r="AE176" s="12"/>
     </row>
-    <row r="177" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="12"/>
       <c r="B177" s="12"/>
       <c r="C177" s="12"/>
@@ -12320,7 +12320,7 @@
       <c r="AD177" s="12"/>
       <c r="AE177" s="12"/>
     </row>
-    <row r="178" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="12"/>
       <c r="B178" s="12"/>
       <c r="C178" s="12"/>
@@ -12359,7 +12359,7 @@
       <c r="AD178" s="12"/>
       <c r="AE178" s="12"/>
     </row>
-    <row r="179" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="12"/>
       <c r="B179" s="12"/>
       <c r="C179" s="12"/>
@@ -12392,7 +12392,7 @@
       <c r="AD179" s="12"/>
       <c r="AE179" s="12"/>
     </row>
-    <row r="180" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12"/>
       <c r="B180" s="12"/>
       <c r="C180" s="12"/>
@@ -12425,7 +12425,7 @@
       <c r="AD180" s="12"/>
       <c r="AE180" s="12"/>
     </row>
-    <row r="181" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="12"/>
       <c r="B181" s="12"/>
       <c r="C181" s="12"/>
@@ -12458,7 +12458,7 @@
       <c r="AD181" s="12"/>
       <c r="AE181" s="12"/>
     </row>
-    <row r="182" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="12"/>
       <c r="B182" s="12"/>
       <c r="C182" s="12"/>
@@ -12491,7 +12491,7 @@
       <c r="AD182" s="12"/>
       <c r="AE182" s="12"/>
     </row>
-    <row r="183" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12"/>
       <c r="B183" s="12"/>
       <c r="C183" s="12"/>
@@ -12524,7 +12524,7 @@
       <c r="AD183" s="12"/>
       <c r="AE183" s="12"/>
     </row>
-    <row r="184" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12"/>
       <c r="B184" s="12"/>
       <c r="C184" s="12"/>
@@ -12557,7 +12557,7 @@
       <c r="AD184" s="12"/>
       <c r="AE184" s="12"/>
     </row>
-    <row r="185" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="12"/>
       <c r="B185" s="12"/>
       <c r="C185" s="12"/>
@@ -12590,7 +12590,7 @@
       <c r="AD185" s="12"/>
       <c r="AE185" s="12"/>
     </row>
-    <row r="186" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="12"/>
       <c r="B186" s="12"/>
       <c r="C186" s="12"/>
@@ -12623,7 +12623,7 @@
       <c r="AD186" s="12"/>
       <c r="AE186" s="12"/>
     </row>
-    <row r="187" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="12"/>
       <c r="B187" s="12"/>
       <c r="C187" s="12"/>
@@ -12656,7 +12656,7 @@
       <c r="AD187" s="12"/>
       <c r="AE187" s="12"/>
     </row>
-    <row r="188" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
       <c r="C188" s="12"/>
@@ -12689,7 +12689,7 @@
       <c r="AD188" s="12"/>
       <c r="AE188" s="12"/>
     </row>
-    <row r="189" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12"/>
       <c r="B189" s="12"/>
       <c r="C189" s="12"/>
@@ -12722,7 +12722,7 @@
       <c r="AD189" s="12"/>
       <c r="AE189" s="12"/>
     </row>
-    <row r="190" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="12"/>
       <c r="B190" s="12"/>
       <c r="C190" s="12"/>
@@ -12755,7 +12755,7 @@
       <c r="AD190" s="12"/>
       <c r="AE190" s="12"/>
     </row>
-    <row r="191" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="12"/>
       <c r="B191" s="12"/>
       <c r="C191" s="12"/>
@@ -12788,7 +12788,7 @@
       <c r="AD191" s="12"/>
       <c r="AE191" s="12"/>
     </row>
-    <row r="192" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
       <c r="C192" s="12"/>
@@ -12821,7 +12821,7 @@
       <c r="AD192" s="12"/>
       <c r="AE192" s="12"/>
     </row>
-    <row r="193" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="12"/>
       <c r="B193" s="12"/>
       <c r="C193" s="12"/>
@@ -12854,7 +12854,7 @@
       <c r="AD193" s="12"/>
       <c r="AE193" s="12"/>
     </row>
-    <row r="194" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="12"/>
       <c r="B194" s="12"/>
       <c r="C194" s="12"/>
@@ -12887,7 +12887,7 @@
       <c r="AD194" s="12"/>
       <c r="AE194" s="12"/>
     </row>
-    <row r="195" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="12"/>
       <c r="B195" s="12"/>
       <c r="C195" s="12"/>
@@ -12920,7 +12920,7 @@
       <c r="AD195" s="12"/>
       <c r="AE195" s="12"/>
     </row>
-    <row r="196" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="12"/>
       <c r="B196" s="12"/>
       <c r="C196" s="12"/>
@@ -12953,7 +12953,7 @@
       <c r="AD196" s="12"/>
       <c r="AE196" s="12"/>
     </row>
-    <row r="197" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="12"/>
       <c r="B197" s="12"/>
       <c r="C197" s="12"/>
@@ -12986,7 +12986,7 @@
       <c r="AD197" s="12"/>
       <c r="AE197" s="12"/>
     </row>
-    <row r="198" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="12"/>
       <c r="B198" s="12"/>
       <c r="C198" s="12"/>
@@ -13019,7 +13019,7 @@
       <c r="AD198" s="12"/>
       <c r="AE198" s="12"/>
     </row>
-    <row r="199" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="12"/>
       <c r="B199" s="12"/>
       <c r="C199" s="12"/>
@@ -13052,7 +13052,7 @@
       <c r="AD199" s="12"/>
       <c r="AE199" s="12"/>
     </row>
-    <row r="200" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="12"/>
       <c r="B200" s="12"/>
       <c r="C200" s="12"/>
@@ -13085,7 +13085,7 @@
       <c r="AD200" s="12"/>
       <c r="AE200" s="12"/>
     </row>
-    <row r="201" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="12"/>
       <c r="B201" s="12"/>
       <c r="C201" s="12"/>
@@ -13118,7 +13118,7 @@
       <c r="AD201" s="12"/>
       <c r="AE201" s="12"/>
     </row>
-    <row r="202" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="12"/>
       <c r="B202" s="12"/>
       <c r="C202" s="12"/>
@@ -13151,7 +13151,7 @@
       <c r="AD202" s="12"/>
       <c r="AE202" s="12"/>
     </row>
-    <row r="203" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="12"/>
       <c r="B203" s="12"/>
       <c r="C203" s="12"/>
@@ -13184,7 +13184,7 @@
       <c r="AD203" s="12"/>
       <c r="AE203" s="12"/>
     </row>
-    <row r="204" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="12"/>
       <c r="B204" s="12"/>
       <c r="C204" s="12"/>
@@ -13217,7 +13217,7 @@
       <c r="AD204" s="12"/>
       <c r="AE204" s="12"/>
     </row>
-    <row r="205" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="12"/>
       <c r="B205" s="12"/>
       <c r="C205" s="12"/>
@@ -13250,7 +13250,7 @@
       <c r="AD205" s="12"/>
       <c r="AE205" s="12"/>
     </row>
-    <row r="206" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="12"/>
       <c r="B206" s="12"/>
       <c r="C206" s="12"/>
@@ -13283,7 +13283,7 @@
       <c r="AD206" s="12"/>
       <c r="AE206" s="12"/>
     </row>
-    <row r="207" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="12"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12"/>
@@ -13316,7 +13316,7 @@
       <c r="AD207" s="12"/>
       <c r="AE207" s="12"/>
     </row>
-    <row r="208" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="12"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12"/>
@@ -13349,7 +13349,7 @@
       <c r="AD208" s="12"/>
       <c r="AE208" s="12"/>
     </row>
-    <row r="209" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="12"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12"/>
@@ -13382,7 +13382,7 @@
       <c r="AD209" s="12"/>
       <c r="AE209" s="12"/>
     </row>
-    <row r="210" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="12"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12"/>
@@ -13415,7 +13415,7 @@
       <c r="AD210" s="12"/>
       <c r="AE210" s="12"/>
     </row>
-    <row r="211" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="12"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12"/>
@@ -13448,7 +13448,7 @@
       <c r="AD211" s="12"/>
       <c r="AE211" s="12"/>
     </row>
-    <row r="212" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="12"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12"/>
@@ -13481,7 +13481,7 @@
       <c r="AD212" s="12"/>
       <c r="AE212" s="12"/>
     </row>
-    <row r="213" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="12"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12"/>
@@ -13514,7 +13514,7 @@
       <c r="AD213" s="12"/>
       <c r="AE213" s="12"/>
     </row>
-    <row r="214" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="12"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
@@ -13547,7 +13547,7 @@
       <c r="AD214" s="12"/>
       <c r="AE214" s="12"/>
     </row>
-    <row r="215" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12"/>
       <c r="B215" s="12"/>
       <c r="C215" s="12"/>
@@ -13580,7 +13580,7 @@
       <c r="AD215" s="12"/>
       <c r="AE215" s="12"/>
     </row>
-    <row r="216" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="12"/>
       <c r="B216" s="12"/>
       <c r="C216" s="12"/>
@@ -13613,7 +13613,7 @@
       <c r="AD216" s="12"/>
       <c r="AE216" s="12"/>
     </row>
-    <row r="217" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="12"/>
       <c r="B217" s="12"/>
       <c r="C217" s="12"/>
@@ -13646,7 +13646,7 @@
       <c r="AD217" s="12"/>
       <c r="AE217" s="12"/>
     </row>
-    <row r="218" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="12"/>
       <c r="B218" s="12"/>
       <c r="C218" s="12"/>
@@ -13679,7 +13679,7 @@
       <c r="AD218" s="12"/>
       <c r="AE218" s="12"/>
     </row>
-    <row r="219" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="12"/>
       <c r="B219" s="12"/>
       <c r="C219" s="12"/>
@@ -13712,7 +13712,7 @@
       <c r="AD219" s="12"/>
       <c r="AE219" s="12"/>
     </row>
-    <row r="220" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="12"/>
       <c r="B220" s="12"/>
       <c r="C220" s="12"/>
@@ -13745,7 +13745,7 @@
       <c r="AD220" s="12"/>
       <c r="AE220" s="12"/>
     </row>
-    <row r="221" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="12"/>
       <c r="B221" s="12"/>
       <c r="C221" s="12"/>
@@ -13778,7 +13778,7 @@
       <c r="AD221" s="12"/>
       <c r="AE221" s="12"/>
     </row>
-    <row r="222" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="12"/>
       <c r="B222" s="12"/>
       <c r="C222" s="12"/>
@@ -13811,7 +13811,7 @@
       <c r="AD222" s="12"/>
       <c r="AE222" s="12"/>
     </row>
-    <row r="223" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="12"/>
       <c r="B223" s="12"/>
       <c r="C223" s="12"/>
@@ -13844,7 +13844,7 @@
       <c r="AD223" s="12"/>
       <c r="AE223" s="12"/>
     </row>
-    <row r="224" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="12"/>
       <c r="B224" s="12"/>
       <c r="C224" s="12"/>
@@ -13877,7 +13877,7 @@
       <c r="AD224" s="12"/>
       <c r="AE224" s="12"/>
     </row>
-    <row r="225" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="12"/>
       <c r="B225" s="12"/>
       <c r="C225" s="12"/>
@@ -13910,7 +13910,7 @@
       <c r="AD225" s="12"/>
       <c r="AE225" s="12"/>
     </row>
-    <row r="226" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="12"/>
       <c r="B226" s="12"/>
       <c r="C226" s="12"/>
@@ -13943,7 +13943,7 @@
       <c r="AD226" s="12"/>
       <c r="AE226" s="12"/>
     </row>
-    <row r="227" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12"/>
       <c r="B227" s="12"/>
       <c r="C227" s="12"/>
@@ -13976,7 +13976,7 @@
       <c r="AD227" s="12"/>
       <c r="AE227" s="12"/>
     </row>
-    <row r="228" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="12"/>
       <c r="B228" s="12"/>
       <c r="C228" s="12"/>
@@ -14009,7 +14009,7 @@
       <c r="AD228" s="12"/>
       <c r="AE228" s="12"/>
     </row>
-    <row r="229" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="12"/>
       <c r="B229" s="12"/>
       <c r="C229" s="12"/>
@@ -14042,7 +14042,7 @@
       <c r="AD229" s="12"/>
       <c r="AE229" s="12"/>
     </row>
-    <row r="230" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="12"/>
       <c r="B230" s="12"/>
       <c r="C230" s="12"/>
@@ -14075,7 +14075,7 @@
       <c r="AD230" s="12"/>
       <c r="AE230" s="12"/>
     </row>
-    <row r="231" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="12"/>
       <c r="B231" s="12"/>
       <c r="C231" s="12"/>
@@ -14108,7 +14108,7 @@
       <c r="AD231" s="12"/>
       <c r="AE231" s="12"/>
     </row>
-    <row r="232" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="12"/>
       <c r="B232" s="12"/>
       <c r="C232" s="12"/>
@@ -14141,7 +14141,7 @@
       <c r="AD232" s="12"/>
       <c r="AE232" s="12"/>
     </row>
-    <row r="233" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="12"/>
       <c r="B233" s="12"/>
       <c r="C233" s="12"/>
@@ -14174,7 +14174,7 @@
       <c r="AD233" s="12"/>
       <c r="AE233" s="12"/>
     </row>
-    <row r="234" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="12"/>
       <c r="B234" s="12"/>
       <c r="C234" s="12"/>
@@ -14207,7 +14207,7 @@
       <c r="AD234" s="12"/>
       <c r="AE234" s="12"/>
     </row>
-    <row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="12"/>
       <c r="B235" s="12"/>
       <c r="C235" s="12"/>
@@ -14240,7 +14240,7 @@
       <c r="AD235" s="12"/>
       <c r="AE235" s="12"/>
     </row>
-    <row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="12"/>
       <c r="B236" s="12"/>
       <c r="C236" s="12"/>
@@ -14273,7 +14273,7 @@
       <c r="AD236" s="12"/>
       <c r="AE236" s="12"/>
     </row>
-    <row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="12"/>
       <c r="B237" s="12"/>
       <c r="C237" s="12"/>
@@ -14306,7 +14306,7 @@
       <c r="AD237" s="12"/>
       <c r="AE237" s="12"/>
     </row>
-    <row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="12"/>
       <c r="B238" s="12"/>
       <c r="C238" s="12"/>
@@ -14339,7 +14339,7 @@
       <c r="AD238" s="12"/>
       <c r="AE238" s="12"/>
     </row>
-    <row r="239" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="12"/>
       <c r="B239" s="12"/>
       <c r="C239" s="12"/>
@@ -14372,7 +14372,7 @@
       <c r="AD239" s="12"/>
       <c r="AE239" s="12"/>
     </row>
-    <row r="240" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="12"/>
       <c r="B240" s="12"/>
       <c r="C240" s="12"/>
@@ -14405,7 +14405,7 @@
       <c r="AD240" s="12"/>
       <c r="AE240" s="12"/>
     </row>
-    <row r="241" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="12"/>
       <c r="B241" s="12"/>
       <c r="C241" s="12"/>
@@ -14438,7 +14438,7 @@
       <c r="AD241" s="12"/>
       <c r="AE241" s="12"/>
     </row>
-    <row r="242" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="12"/>
       <c r="B242" s="12"/>
       <c r="C242" s="12"/>
@@ -14471,7 +14471,7 @@
       <c r="AD242" s="12"/>
       <c r="AE242" s="12"/>
     </row>
-    <row r="243" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="12"/>
       <c r="B243" s="12"/>
       <c r="C243" s="12"/>
@@ -14504,7 +14504,7 @@
       <c r="AD243" s="12"/>
       <c r="AE243" s="12"/>
     </row>
-    <row r="244" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="12"/>
       <c r="B244" s="12"/>
       <c r="C244" s="12"/>
@@ -14537,7 +14537,7 @@
       <c r="AD244" s="12"/>
       <c r="AE244" s="12"/>
     </row>
-    <row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="12"/>
       <c r="B245" s="12"/>
       <c r="C245" s="12"/>
@@ -14570,7 +14570,7 @@
       <c r="AD245" s="12"/>
       <c r="AE245" s="12"/>
     </row>
-    <row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="12"/>
       <c r="B246" s="12"/>
       <c r="C246" s="12"/>
@@ -14603,7 +14603,7 @@
       <c r="AD246" s="12"/>
       <c r="AE246" s="12"/>
     </row>
-    <row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="12"/>
       <c r="B247" s="12"/>
       <c r="C247" s="12"/>
@@ -14636,7 +14636,7 @@
       <c r="AD247" s="12"/>
       <c r="AE247" s="12"/>
     </row>
-    <row r="248" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="12"/>
       <c r="B248" s="12"/>
       <c r="C248" s="12"/>
@@ -14669,7 +14669,7 @@
       <c r="AD248" s="12"/>
       <c r="AE248" s="12"/>
     </row>
-    <row r="249" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="12"/>
       <c r="B249" s="12"/>
       <c r="C249" s="12"/>
@@ -14702,7 +14702,7 @@
       <c r="AD249" s="12"/>
       <c r="AE249" s="12"/>
     </row>
-    <row r="250" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="12"/>
       <c r="B250" s="12"/>
       <c r="C250" s="12"/>
@@ -14735,7 +14735,7 @@
       <c r="AD250" s="12"/>
       <c r="AE250" s="12"/>
     </row>
-    <row r="251" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="12"/>
       <c r="B251" s="12"/>
       <c r="C251" s="12"/>
@@ -14768,7 +14768,7 @@
       <c r="AD251" s="12"/>
       <c r="AE251" s="12"/>
     </row>
-    <row r="252" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="12"/>
       <c r="B252" s="12"/>
       <c r="C252" s="12"/>
@@ -14801,7 +14801,7 @@
       <c r="AD252" s="12"/>
       <c r="AE252" s="12"/>
     </row>
-    <row r="253" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="12"/>
       <c r="B253" s="12"/>
       <c r="C253" s="12"/>
@@ -14834,7 +14834,7 @@
       <c r="AD253" s="12"/>
       <c r="AE253" s="12"/>
     </row>
-    <row r="254" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="12"/>
       <c r="B254" s="12"/>
       <c r="C254" s="12"/>
@@ -14867,7 +14867,7 @@
       <c r="AD254" s="12"/>
       <c r="AE254" s="12"/>
     </row>
-    <row r="255" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="12"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
@@ -14900,7 +14900,7 @@
       <c r="AD255" s="12"/>
       <c r="AE255" s="12"/>
     </row>
-    <row r="256" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="12"/>
       <c r="B256" s="12"/>
       <c r="C256" s="12"/>
@@ -14933,7 +14933,7 @@
       <c r="AD256" s="12"/>
       <c r="AE256" s="12"/>
     </row>
-    <row r="257" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="12"/>
       <c r="B257" s="12"/>
       <c r="C257" s="12"/>
@@ -14966,7 +14966,7 @@
       <c r="AD257" s="12"/>
       <c r="AE257" s="12"/>
     </row>
-    <row r="258" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="12"/>
       <c r="B258" s="12"/>
       <c r="C258" s="12"/>
@@ -14999,7 +14999,7 @@
       <c r="AD258" s="12"/>
       <c r="AE258" s="12"/>
     </row>
-    <row r="259" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="12"/>
       <c r="B259" s="12"/>
       <c r="C259" s="12"/>
@@ -15032,7 +15032,7 @@
       <c r="AD259" s="12"/>
       <c r="AE259" s="12"/>
     </row>
-    <row r="260" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="12"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12"/>
@@ -15065,7 +15065,7 @@
       <c r="AD260" s="12"/>
       <c r="AE260" s="12"/>
     </row>
-    <row r="261" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="12"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12"/>
@@ -15098,7 +15098,7 @@
       <c r="AD261" s="12"/>
       <c r="AE261" s="12"/>
     </row>
-    <row r="262" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="12"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12"/>
@@ -15131,7 +15131,7 @@
       <c r="AD262" s="12"/>
       <c r="AE262" s="12"/>
     </row>
-    <row r="263" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="12"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
@@ -15164,7 +15164,7 @@
       <c r="AD263" s="12"/>
       <c r="AE263" s="12"/>
     </row>
-    <row r="264" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="12"/>
       <c r="B264" s="12"/>
       <c r="C264" s="12"/>
@@ -15197,7 +15197,7 @@
       <c r="AD264" s="12"/>
       <c r="AE264" s="12"/>
     </row>
-    <row r="265" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="12"/>
       <c r="B265" s="12"/>
       <c r="C265" s="12"/>
@@ -15230,7 +15230,7 @@
       <c r="AD265" s="12"/>
       <c r="AE265" s="12"/>
     </row>
-    <row r="266" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="12"/>
       <c r="B266" s="12"/>
       <c r="C266" s="12"/>
@@ -15263,7 +15263,7 @@
       <c r="AD266" s="12"/>
       <c r="AE266" s="12"/>
     </row>
-    <row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="12"/>
       <c r="B267" s="12"/>
       <c r="C267" s="12"/>
@@ -15296,7 +15296,7 @@
       <c r="AD267" s="12"/>
       <c r="AE267" s="12"/>
     </row>
-    <row r="268" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="12"/>
       <c r="B268" s="12"/>
       <c r="C268" s="12"/>
@@ -15329,7 +15329,7 @@
       <c r="AD268" s="12"/>
       <c r="AE268" s="12"/>
     </row>
-    <row r="269" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="12"/>
       <c r="B269" s="12"/>
       <c r="C269" s="12"/>
@@ -15362,7 +15362,7 @@
       <c r="AD269" s="12"/>
       <c r="AE269" s="12"/>
     </row>
-    <row r="270" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="12"/>
       <c r="B270" s="12"/>
       <c r="C270" s="12"/>
@@ -15395,7 +15395,7 @@
       <c r="AD270" s="12"/>
       <c r="AE270" s="12"/>
     </row>
-    <row r="271" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="12"/>
       <c r="B271" s="12"/>
       <c r="C271" s="12"/>
@@ -15428,7 +15428,7 @@
       <c r="AD271" s="12"/>
       <c r="AE271" s="12"/>
     </row>
-    <row r="272" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="12"/>
       <c r="B272" s="12"/>
       <c r="C272" s="12"/>
@@ -15461,7 +15461,7 @@
       <c r="AD272" s="12"/>
       <c r="AE272" s="12"/>
     </row>
-    <row r="273" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="12"/>
       <c r="B273" s="12"/>
       <c r="C273" s="12"/>
@@ -15494,7 +15494,7 @@
       <c r="AD273" s="12"/>
       <c r="AE273" s="12"/>
     </row>
-    <row r="274" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
@@ -15527,7 +15527,7 @@
       <c r="AD274" s="12"/>
       <c r="AE274" s="12"/>
     </row>
-    <row r="275" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
@@ -15560,7 +15560,7 @@
       <c r="AD275" s="12"/>
       <c r="AE275" s="12"/>
     </row>
-    <row r="276" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
@@ -15593,7 +15593,7 @@
       <c r="AD276" s="12"/>
       <c r="AE276" s="12"/>
     </row>
-    <row r="277" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
@@ -15626,7 +15626,7 @@
       <c r="AD277" s="12"/>
       <c r="AE277" s="12"/>
     </row>
-    <row r="278" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
@@ -15659,7 +15659,7 @@
       <c r="AD278" s="12"/>
       <c r="AE278" s="12"/>
     </row>
-    <row r="279" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12"/>
@@ -15692,7 +15692,7 @@
       <c r="AD279" s="12"/>
       <c r="AE279" s="12"/>
     </row>
-    <row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
@@ -15725,7 +15725,7 @@
       <c r="AD280" s="12"/>
       <c r="AE280" s="12"/>
     </row>
-    <row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
@@ -15758,7 +15758,7 @@
       <c r="AD281" s="12"/>
       <c r="AE281" s="12"/>
     </row>
-    <row r="282" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
@@ -15791,7 +15791,7 @@
       <c r="AD282" s="12"/>
       <c r="AE282" s="12"/>
     </row>
-    <row r="283" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
@@ -15824,7 +15824,7 @@
       <c r="AD283" s="12"/>
       <c r="AE283" s="12"/>
     </row>
-    <row r="284" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
@@ -15857,7 +15857,7 @@
       <c r="AD284" s="12"/>
       <c r="AE284" s="12"/>
     </row>
-    <row r="285" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="12"/>
       <c r="B285" s="12"/>
       <c r="C285" s="12"/>
@@ -15890,7 +15890,7 @@
       <c r="AD285" s="12"/>
       <c r="AE285" s="12"/>
     </row>
-    <row r="286" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="12"/>
       <c r="B286" s="12"/>
       <c r="C286" s="12"/>
@@ -15923,7 +15923,7 @@
       <c r="AD286" s="12"/>
       <c r="AE286" s="12"/>
     </row>
-    <row r="287" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="12"/>
       <c r="B287" s="12"/>
       <c r="C287" s="12"/>
@@ -15956,7 +15956,7 @@
       <c r="AD287" s="12"/>
       <c r="AE287" s="12"/>
     </row>
-    <row r="288" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="12"/>
       <c r="B288" s="12"/>
       <c r="C288" s="12"/>
@@ -15989,7 +15989,7 @@
       <c r="AD288" s="12"/>
       <c r="AE288" s="12"/>
     </row>
-    <row r="289" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="12"/>
       <c r="B289" s="12"/>
       <c r="C289" s="12"/>
@@ -16022,7 +16022,7 @@
       <c r="AD289" s="12"/>
       <c r="AE289" s="12"/>
     </row>
-    <row r="290" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="12"/>
       <c r="B290" s="12"/>
       <c r="C290" s="12"/>
@@ -16055,7 +16055,7 @@
       <c r="AD290" s="12"/>
       <c r="AE290" s="12"/>
     </row>
-    <row r="291" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="12"/>
       <c r="B291" s="12"/>
       <c r="C291" s="12"/>
@@ -16088,7 +16088,7 @@
       <c r="AD291" s="12"/>
       <c r="AE291" s="12"/>
     </row>
-    <row r="292" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="12"/>
       <c r="B292" s="12"/>
       <c r="C292" s="12"/>
@@ -16121,7 +16121,7 @@
       <c r="AD292" s="12"/>
       <c r="AE292" s="12"/>
     </row>
-    <row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="12"/>
       <c r="B293" s="12"/>
       <c r="C293" s="12"/>
@@ -16154,7 +16154,7 @@
       <c r="AD293" s="12"/>
       <c r="AE293" s="12"/>
     </row>
-    <row r="294" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="12"/>
       <c r="B294" s="12"/>
       <c r="C294" s="12"/>
@@ -16187,7 +16187,7 @@
       <c r="AD294" s="12"/>
       <c r="AE294" s="12"/>
     </row>
-    <row r="295" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="12"/>
       <c r="B295" s="12"/>
       <c r="C295" s="12"/>
@@ -16220,7 +16220,7 @@
       <c r="AD295" s="12"/>
       <c r="AE295" s="12"/>
     </row>
-    <row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12"/>
@@ -16253,7 +16253,7 @@
       <c r="AD296" s="12"/>
       <c r="AE296" s="12"/>
     </row>
-    <row r="297" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12"/>
@@ -16286,7 +16286,7 @@
       <c r="AD297" s="12"/>
       <c r="AE297" s="12"/>
     </row>
-    <row r="298" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="12"/>
       <c r="B298" s="12"/>
       <c r="C298" s="12"/>
@@ -16319,7 +16319,7 @@
       <c r="AD298" s="12"/>
       <c r="AE298" s="12"/>
     </row>
-    <row r="299" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12"/>
@@ -16352,7 +16352,7 @@
       <c r="AD299" s="12"/>
       <c r="AE299" s="12"/>
     </row>
-    <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="12" t="str">
         <f>M9</f>
         <v>Tsjekkia</v>
@@ -16403,7 +16403,7 @@
       <c r="AD300" s="12"/>
       <c r="AE300" s="12"/>
     </row>
-    <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="12" t="str">
         <f>M17</f>
         <v>Bosnia-Hercegovina</v>
@@ -16454,7 +16454,7 @@
       <c r="AD301" s="12"/>
       <c r="AE301" s="12"/>
     </row>
-    <row r="302" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="12" t="str">
         <f>M25</f>
         <v>Skottland</v>
@@ -16505,7 +16505,7 @@
       <c r="AD302" s="12"/>
       <c r="AE302" s="12"/>
     </row>
-    <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="12" t="str">
         <f>M33</f>
         <v>Paraguay</v>
@@ -16556,7 +16556,7 @@
       <c r="AD303" s="12"/>
       <c r="AE303" s="12"/>
     </row>
-    <row r="304" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="12" t="str">
         <f>M41</f>
         <v>Elfenbenskysten</v>
@@ -16607,7 +16607,7 @@
       <c r="AD304" s="12"/>
       <c r="AE304" s="12"/>
     </row>
-    <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="12" t="str">
         <f>M49</f>
         <v>Sverige</v>
@@ -16658,7 +16658,7 @@
       <c r="AD305" s="12"/>
       <c r="AE305" s="12"/>
     </row>
-    <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="12" t="str">
         <f>M57</f>
         <v>Iran</v>
@@ -16709,7 +16709,7 @@
       <c r="AD306" s="12"/>
       <c r="AE306" s="12"/>
     </row>
-    <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="12" t="str">
         <f>M65</f>
         <v>Saudi Arabia</v>
@@ -16760,7 +16760,7 @@
       <c r="AD307" s="12"/>
       <c r="AE307" s="12"/>
     </row>
-    <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="12" t="str">
         <f>M73</f>
         <v>Senegal</v>
@@ -16811,7 +16811,7 @@
       <c r="AD308" s="12"/>
       <c r="AE308" s="12"/>
     </row>
-    <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="12" t="str">
         <f>M81</f>
         <v>Algerie</v>
@@ -16862,7 +16862,7 @@
       <c r="AD309" s="12"/>
       <c r="AE309" s="12"/>
     </row>
-    <row r="310" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="12" t="str">
         <f>M89</f>
         <v>Usbekistan</v>
@@ -16913,7 +16913,7 @@
       <c r="AD310" s="12"/>
       <c r="AE310" s="12"/>
     </row>
-    <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="12" t="str">
         <f>M97</f>
         <v>Ghana</v>
@@ -16964,7 +16964,7 @@
       <c r="AD311" s="12"/>
       <c r="AE311" s="12"/>
     </row>
-    <row r="320" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>141</v>
       </c>
@@ -16972,7 +16972,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>140</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>82</v>
       </c>
@@ -16988,7 +16988,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>112</v>
       </c>
@@ -16996,7 +16996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>53</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>67</v>
       </c>
@@ -17012,7 +17012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>52</v>
       </c>
@@ -17020,7 +17020,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>150</v>
       </c>
@@ -17028,7 +17028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>90</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>148</v>
       </c>
@@ -17044,7 +17044,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="330" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>94</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>113</v>
       </c>
@@ -17060,7 +17060,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>93</v>
       </c>
@@ -17068,7 +17068,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>155</v>
       </c>
@@ -17076,7 +17076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>130</v>
       </c>
@@ -17084,7 +17084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>157</v>
       </c>
@@ -17092,7 +17092,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>71</v>
       </c>
@@ -17100,7 +17100,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>132</v>
       </c>
@@ -17108,7 +17108,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>105</v>
       </c>
@@ -17116,7 +17116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>143</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="340" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>124</v>
       </c>
@@ -17132,7 +17132,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="341" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>156</v>
       </c>
@@ -17140,7 +17140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>168</v>
       </c>
@@ -17148,7 +17148,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>68</v>
       </c>
@@ -17156,7 +17156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="344" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>28</v>
       </c>
@@ -17164,7 +17164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="345" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>104</v>
       </c>
@@ -17172,7 +17172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>115</v>
       </c>
@@ -17180,7 +17180,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>133</v>
       </c>
@@ -17188,7 +17188,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>158</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>81</v>
       </c>
@@ -17204,7 +17204,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>147</v>
       </c>
@@ -17212,7 +17212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>55</v>
       </c>
@@ -17220,7 +17220,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>125</v>
       </c>
@@ -17228,7 +17228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="353" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>131</v>
       </c>
@@ -17236,7 +17236,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="354" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>72</v>
       </c>
@@ -17244,7 +17244,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="355" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>123</v>
       </c>
@@ -17252,7 +17252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>56</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="357" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>107</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="358" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>30</v>
       </c>
@@ -17276,7 +17276,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="359" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>35</v>
       </c>
@@ -17284,7 +17284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="360" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>36</v>
       </c>
@@ -17292,7 +17292,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="361" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>108</v>
       </c>
@@ -17300,7 +17300,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="362" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>83</v>
       </c>
@@ -17308,7 +17308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>89</v>
       </c>
@@ -17316,7 +17316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="364" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>80</v>
       </c>
@@ -17324,7 +17324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="365" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>126</v>
       </c>
@@ -17332,7 +17332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="366" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>149</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="367" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>142</v>
       </c>
@@ -17350,6 +17350,35 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="M1:U1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="M2:U2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="M3:U3"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="M21:U21"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="M29:U29"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="M37:U37"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="M53:U53"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="M61:U61"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="M77:U77"/>
+    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="M85:U85"/>
     <mergeCell ref="I157:K157"/>
     <mergeCell ref="I168:K168"/>
     <mergeCell ref="I175:K175"/>
@@ -17358,35 +17387,6 @@
     <mergeCell ref="H101:K101"/>
     <mergeCell ref="I103:K103"/>
     <mergeCell ref="I138:K138"/>
-    <mergeCell ref="A69:K69"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="M77:U77"/>
-    <mergeCell ref="A85:K85"/>
-    <mergeCell ref="M85:U85"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A53:K53"/>
-    <mergeCell ref="M53:U53"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="M61:U61"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="M21:U21"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="M29:U29"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="M37:U37"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="M3:U3"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="M1:U1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="M2:U2"/>
   </mergeCells>
   <conditionalFormatting sqref="H105:H136">
     <cfRule type="expression" dxfId="19" priority="2">
@@ -17468,7 +17468,7 @@
       <formula>AND(COUNTIF($H$177:$H$178,1)&gt;=1,$H177&lt;&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="5">
+  <dataValidations count="5">
     <dataValidation type="whole" operator="equal" allowBlank="1" errorTitle="Ugyldig verdi" error="Kun 1 er tillatt (eller la cellen stå tom)" promptTitle="Går laget videre?" prompt="Skriv 1 for å velge laget (maks 16 i denne runden)" sqref="H105:H136" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>0</formula2>
@@ -17754,15 +17754,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9cd4a677-7aee-4d17-8718-d38c4fab49a7">
@@ -17771,6 +17762,15 @@
     <TaxCatchAll xmlns="d4f56ad3-4be4-4368-a565-df4965c1e22f" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17793,14 +17793,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD46F970-DEC9-4AF4-95E8-BA2A2F98E5F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5289171D-7414-480A-A6B0-4629BA2371E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17809,4 +17801,12 @@
     <ds:schemaRef ds:uri="d4f56ad3-4be4-4368-a565-df4965c1e22f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD46F970-DEC9-4AF4-95E8-BA2A2F98E5F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>